--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9325" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9325" uniqueCount="805">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -982,10 +982,6 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -1038,9 +1034,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://fhir.de/CodeSystem/ifa/pzn</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1169,9 +1162,6 @@
   </si>
   <si>
     <t>MedicationKnowledge.extension:wechselwirkungen.extension:wechselwirkungserfassung_Code.value[x]:valueCodeableConcept.coding:snomed.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
   </si>
   <si>
     <t>MedicationKnowledge.extension:wechselwirkungen.extension:wechselwirkungserfassung_Code.value[x]:valueCodeableConcept.coding:snomed.version</t>
@@ -9634,7 +9624,7 @@
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>310</v>
+        <v>217</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
@@ -9644,7 +9634,7 @@
         <v>114</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9659,27 +9649,27 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>305</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>77</v>
@@ -9704,10 +9694,10 @@
         <v>145</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>308</v>
@@ -9762,7 +9752,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9777,24 +9767,24 @@
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9903,10 +9893,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10017,10 +10007,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10046,16 +10036,16 @@
         <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -10065,7 +10055,7 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>77</v>
@@ -10104,7 +10094,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10119,7 +10109,7 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
@@ -10128,15 +10118,15 @@
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10162,13 +10152,13 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10218,7 +10208,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10233,7 +10223,7 @@
         <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>77</v>
@@ -10242,15 +10232,15 @@
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10276,16 +10266,16 @@
         <v>169</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10334,7 +10324,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10349,7 +10339,7 @@
         <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
@@ -10358,15 +10348,15 @@
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10392,16 +10382,16 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10450,7 +10440,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10465,7 +10455,7 @@
         <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>77</v>
@@ -10474,15 +10464,15 @@
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10505,19 +10495,19 @@
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10566,7 +10556,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10581,7 +10571,7 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>77</v>
@@ -10590,18 +10580,18 @@
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>305</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>77</v>
@@ -10684,7 +10674,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10699,24 +10689,24 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10825,10 +10815,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10939,10 +10929,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10968,16 +10958,16 @@
         <v>129</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10987,7 +10977,7 @@
         <v>77</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>77</v>
@@ -11026,7 +11016,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11041,7 +11031,7 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>77</v>
@@ -11050,15 +11040,15 @@
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11084,13 +11074,13 @@
         <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11140,7 +11130,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11155,7 +11145,7 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>77</v>
@@ -11164,15 +11154,15 @@
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11198,16 +11188,16 @@
         <v>169</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11256,7 +11246,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11271,7 +11261,7 @@
         <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>77</v>
@@ -11280,15 +11270,15 @@
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11314,16 +11304,16 @@
         <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11372,7 +11362,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11387,7 +11377,7 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>77</v>
@@ -11396,15 +11386,15 @@
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11427,19 +11417,19 @@
         <v>86</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -11488,7 +11478,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11503,7 +11493,7 @@
         <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>77</v>
@@ -11512,15 +11502,15 @@
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11546,16 +11536,16 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -11604,7 +11594,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11619,7 +11609,7 @@
         <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>77</v>
@@ -11628,12 +11618,12 @@
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>207</v>
@@ -11676,7 +11666,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>77</v>
@@ -11747,7 +11737,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>214</v>
@@ -11773,7 +11763,7 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>215</v>
@@ -11859,13 +11849,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>77</v>
@@ -11887,13 +11877,13 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11973,7 +11963,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>203</v>
@@ -12085,7 +12075,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>205</v>
@@ -12197,7 +12187,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>207</v>
@@ -12240,7 +12230,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>77</v>
@@ -12311,7 +12301,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>214</v>
@@ -12421,7 +12411,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>214</v>
@@ -12535,10 +12525,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12647,10 +12637,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12761,10 +12751,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12846,7 +12836,7 @@
         <v>195</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12861,27 +12851,27 @@
         <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>77</v>
@@ -12964,7 +12954,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12979,24 +12969,24 @@
         <v>98</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13105,10 +13095,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13219,10 +13209,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13248,16 +13238,16 @@
         <v>129</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -13267,7 +13257,7 @@
         <v>77</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>77</v>
@@ -13306,7 +13296,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13321,7 +13311,7 @@
         <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>77</v>
@@ -13330,15 +13320,15 @@
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13364,13 +13354,13 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13420,7 +13410,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13435,7 +13425,7 @@
         <v>98</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>77</v>
@@ -13444,15 +13434,15 @@
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13478,16 +13468,16 @@
         <v>169</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -13536,7 +13526,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13551,7 +13541,7 @@
         <v>98</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>77</v>
@@ -13560,15 +13550,15 @@
         <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13594,16 +13584,16 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13652,7 +13642,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13667,7 +13657,7 @@
         <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>77</v>
@@ -13676,15 +13666,15 @@
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13707,19 +13697,19 @@
         <v>86</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -13768,7 +13758,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13783,7 +13773,7 @@
         <v>98</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>77</v>
@@ -13792,15 +13782,15 @@
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13826,16 +13816,16 @@
         <v>101</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13884,7 +13874,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13899,7 +13889,7 @@
         <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>77</v>
@@ -13908,18 +13898,18 @@
         <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>77</v>
@@ -13941,13 +13931,13 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14027,7 +14017,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>203</v>
@@ -14139,7 +14129,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>205</v>
@@ -14253,13 +14243,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>77</v>
@@ -14367,7 +14357,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>232</v>
@@ -14479,7 +14469,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>234</v>
@@ -14591,7 +14581,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>236</v>
@@ -14634,7 +14624,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>77</v>
@@ -14705,7 +14695,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>238</v>
@@ -14815,7 +14805,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>238</v>
@@ -14846,13 +14836,13 @@
         <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>216</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14931,13 +14921,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>77</v>
@@ -15045,7 +15035,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>232</v>
@@ -15157,7 +15147,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>234</v>
@@ -15269,7 +15259,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>236</v>
@@ -15312,7 +15302,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>77</v>
@@ -15383,7 +15373,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>238</v>
@@ -15493,7 +15483,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>238</v>
@@ -15521,7 +15511,7 @@
         <v>77</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>215</v>
@@ -15607,7 +15597,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>260</v>
@@ -15719,7 +15709,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>262</v>
@@ -15833,7 +15823,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>264</v>
@@ -15947,7 +15937,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>271</v>
@@ -16061,7 +16051,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>279</v>
@@ -16175,7 +16165,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>288</v>
@@ -16289,7 +16279,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>207</v>
@@ -16332,7 +16322,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>77</v>
@@ -16403,7 +16393,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>214</v>
@@ -16429,7 +16419,7 @@
         <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>215</v>
@@ -16515,10 +16505,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16544,16 +16534,16 @@
         <v>108</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>77</v>
@@ -16602,7 +16592,7 @@
         <v>114</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16631,10 +16621,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16660,13 +16650,13 @@
         <v>299</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16695,10 +16685,10 @@
         <v>159</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>77</v>
@@ -16716,7 +16706,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16731,24 +16721,24 @@
         <v>98</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16857,10 +16847,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16971,10 +16961,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17046,7 +17036,7 @@
         <v>77</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>310</v>
+        <v>139</v>
       </c>
       <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
@@ -17056,7 +17046,7 @@
         <v>114</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17071,27 +17061,27 @@
         <v>98</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>77</v>
@@ -17116,10 +17106,10 @@
         <v>145</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>308</v>
@@ -17174,7 +17164,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17189,24 +17179,24 @@
         <v>98</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN126" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17315,10 +17305,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17429,10 +17419,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17458,16 +17448,16 @@
         <v>129</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -17477,7 +17467,7 @@
         <v>77</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>77</v>
@@ -17516,7 +17506,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17531,7 +17521,7 @@
         <v>98</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>77</v>
@@ -17540,15 +17530,15 @@
         <v>77</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17574,13 +17564,13 @@
         <v>101</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17630,7 +17620,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17645,7 +17635,7 @@
         <v>98</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>77</v>
@@ -17654,15 +17644,15 @@
         <v>77</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17688,16 +17678,16 @@
         <v>169</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -17746,7 +17736,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17761,7 +17751,7 @@
         <v>98</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>77</v>
@@ -17770,15 +17760,15 @@
         <v>77</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17804,16 +17794,16 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O132" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -17862,7 +17852,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17877,7 +17867,7 @@
         <v>98</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>77</v>
@@ -17886,15 +17876,15 @@
         <v>77</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17917,19 +17907,19 @@
         <v>86</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -17978,7 +17968,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17993,7 +17983,7 @@
         <v>98</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>77</v>
@@ -18002,15 +17992,15 @@
         <v>77</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18036,16 +18026,16 @@
         <v>101</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>77</v>
@@ -18094,7 +18084,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -18109,7 +18099,7 @@
         <v>98</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>77</v>
@@ -18118,15 +18108,15 @@
         <v>77</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18152,13 +18142,13 @@
         <v>169</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18184,13 +18174,13 @@
         <v>77</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -18208,7 +18198,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18223,7 +18213,7 @@
         <v>98</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>77</v>
@@ -18237,10 +18227,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18263,16 +18253,16 @@
         <v>86</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N136" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18322,7 +18312,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18334,27 +18324,27 @@
         <v>97</v>
       </c>
       <c r="AJ136" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AK136" t="s" s="2">
+      <c r="AN136" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>511</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18380,13 +18370,13 @@
         <v>299</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18415,10 +18405,10 @@
         <v>159</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>77</v>
@@ -18436,7 +18426,7 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18451,24 +18441,24 @@
         <v>98</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18491,16 +18481,16 @@
         <v>86</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N138" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18550,7 +18540,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18562,10 +18552,10 @@
         <v>97</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>77</v>
@@ -18574,15 +18564,15 @@
         <v>77</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18608,13 +18598,13 @@
         <v>101</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18664,7 +18654,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18693,10 +18683,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18719,13 +18709,13 @@
         <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18776,7 +18766,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18805,10 +18795,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18917,10 +18907,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19031,14 +19021,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19060,16 +19050,16 @@
         <v>108</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>77</v>
@@ -19118,7 +19108,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -19147,10 +19137,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19176,13 +19166,13 @@
         <v>299</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19232,7 +19222,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>85</v>
@@ -19247,7 +19237,7 @@
         <v>98</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>77</v>
@@ -19256,15 +19246,15 @@
         <v>77</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19287,16 +19277,16 @@
         <v>77</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -19346,7 +19336,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>85</v>
@@ -19358,10 +19348,10 @@
         <v>97</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>77</v>
@@ -19375,10 +19365,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19401,16 +19391,16 @@
         <v>77</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -19460,7 +19450,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19472,10 +19462,10 @@
         <v>97</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>77</v>
@@ -19489,10 +19479,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19518,13 +19508,13 @@
         <v>299</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19574,7 +19564,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19589,7 +19579,7 @@
         <v>98</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>77</v>
@@ -19598,15 +19588,15 @@
         <v>77</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19629,13 +19619,13 @@
         <v>77</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19686,7 +19676,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19715,10 +19705,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19827,10 +19817,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19941,14 +19931,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19970,16 +19960,16 @@
         <v>108</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -20028,7 +20018,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -20057,10 +20047,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20086,13 +20076,13 @@
         <v>299</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20142,7 +20132,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -20157,7 +20147,7 @@
         <v>98</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>77</v>
@@ -20166,15 +20156,15 @@
         <v>77</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20197,16 +20187,16 @@
         <v>77</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -20256,7 +20246,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20268,10 +20258,10 @@
         <v>97</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>77</v>
@@ -20285,10 +20275,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20397,10 +20387,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20511,10 +20501,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20625,10 +20615,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20739,10 +20729,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20853,10 +20843,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20967,10 +20957,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20993,13 +20983,13 @@
         <v>77</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21050,7 +21040,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -21079,10 +21069,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21191,10 +21181,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21305,14 +21295,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -21334,16 +21324,16 @@
         <v>108</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -21392,7 +21382,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21421,10 +21411,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21447,13 +21437,13 @@
         <v>77</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -21502,7 +21492,7 @@
         <v>114</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>85</v>
@@ -21517,27 +21507,27 @@
         <v>98</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>77</v>
@@ -21559,13 +21549,13 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -21616,7 +21606,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>85</v>
@@ -21631,24 +21621,24 @@
         <v>98</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21671,17 +21661,17 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21730,7 +21720,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21745,7 +21735,7 @@
         <v>98</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>77</v>
@@ -21759,10 +21749,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21785,16 +21775,16 @@
         <v>77</v>
       </c>
       <c r="K167" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="L167" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -21844,7 +21834,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21856,27 +21846,27 @@
         <v>97</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21899,16 +21889,16 @@
         <v>77</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -21958,7 +21948,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21987,10 +21977,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22016,13 +22006,13 @@
         <v>299</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -22051,10 +22041,10 @@
         <v>159</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>77</v>
@@ -22072,7 +22062,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -22087,7 +22077,7 @@
         <v>98</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>77</v>
@@ -22096,15 +22086,15 @@
         <v>77</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22127,13 +22117,13 @@
         <v>77</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22184,7 +22174,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -22213,10 +22203,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22325,10 +22315,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22439,14 +22429,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -22468,16 +22458,16 @@
         <v>108</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -22526,7 +22516,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22555,10 +22545,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22584,13 +22574,13 @@
         <v>299</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -22620,7 +22610,7 @@
       </c>
       <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>77</v>
@@ -22638,7 +22628,7 @@
         <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>85</v>
@@ -22653,7 +22643,7 @@
         <v>98</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>77</v>
@@ -22662,15 +22652,15 @@
         <v>77</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22696,13 +22686,13 @@
         <v>101</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -22752,7 +22742,7 @@
         <v>77</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -22781,10 +22771,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22807,13 +22797,13 @@
         <v>77</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22864,7 +22854,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>85</v>
@@ -22879,7 +22869,7 @@
         <v>98</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>77</v>
@@ -22893,10 +22883,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22919,13 +22909,13 @@
         <v>77</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -22976,7 +22966,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
@@ -23005,10 +22995,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23117,10 +23107,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23231,14 +23221,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -23260,16 +23250,16 @@
         <v>108</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N180" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -23318,7 +23308,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -23347,10 +23337,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23376,13 +23366,13 @@
         <v>299</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -23432,7 +23422,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -23447,7 +23437,7 @@
         <v>98</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>77</v>
@@ -23456,15 +23446,15 @@
         <v>77</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23490,13 +23480,13 @@
         <v>101</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -23546,7 +23536,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>78</v>
@@ -23575,10 +23565,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23601,13 +23591,13 @@
         <v>77</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -23658,7 +23648,7 @@
         <v>77</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>78</v>
@@ -23687,10 +23677,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23799,10 +23789,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23913,14 +23903,14 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -23942,16 +23932,16 @@
         <v>108</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N186" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
@@ -24000,7 +23990,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -24029,10 +24019,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24055,13 +24045,13 @@
         <v>77</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -24112,7 +24102,7 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -24141,10 +24131,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24253,10 +24243,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24367,14 +24357,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -24396,16 +24386,16 @@
         <v>108</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>77</v>
@@ -24454,7 +24444,7 @@
         <v>77</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>78</v>
@@ -24483,10 +24473,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24512,13 +24502,13 @@
         <v>299</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -24568,7 +24558,7 @@
         <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>85</v>
@@ -24583,7 +24573,7 @@
         <v>98</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>77</v>
@@ -24592,15 +24582,15 @@
         <v>77</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24623,13 +24613,13 @@
         <v>77</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -24680,7 +24670,7 @@
         <v>77</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>85</v>
@@ -24695,7 +24685,7 @@
         <v>98</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>77</v>
@@ -24709,10 +24699,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24738,10 +24728,10 @@
         <v>299</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -24790,7 +24780,7 @@
         <v>114</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
@@ -24819,10 +24809,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24931,10 +24921,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25043,10 +25033,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25128,7 +25118,7 @@
         <v>114</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -25143,27 +25133,27 @@
         <v>98</v>
       </c>
       <c r="AK196" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN196" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>77</v>
@@ -25246,7 +25236,7 @@
         <v>77</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -25261,24 +25251,24 @@
         <v>98</v>
       </c>
       <c r="AK197" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN197" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL197" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM197" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN197" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25387,10 +25377,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25499,10 +25489,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25528,16 +25518,16 @@
         <v>129</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M200" t="s" s="2">
+      <c r="N200" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N200" t="s" s="2">
+      <c r="O200" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>77</v>
@@ -25547,7 +25537,7 @@
         <v>77</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>77</v>
@@ -25586,7 +25576,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -25601,7 +25591,7 @@
         <v>98</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>77</v>
@@ -25610,15 +25600,15 @@
         <v>77</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25644,13 +25634,13 @@
         <v>101</v>
       </c>
       <c r="L201" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M201" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N201" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -25700,7 +25690,7 @@
         <v>77</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>78</v>
@@ -25715,7 +25705,7 @@
         <v>98</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL201" t="s" s="2">
         <v>77</v>
@@ -25724,15 +25714,15 @@
         <v>77</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25758,16 +25748,16 @@
         <v>169</v>
       </c>
       <c r="L202" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M202" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N202" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M202" t="s" s="2">
+      <c r="O202" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>77</v>
@@ -25816,7 +25806,7 @@
         <v>77</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>78</v>
@@ -25831,7 +25821,7 @@
         <v>98</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>77</v>
@@ -25840,15 +25830,15 @@
         <v>77</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25874,16 +25864,16 @@
         <v>101</v>
       </c>
       <c r="L203" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M203" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O203" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>77</v>
@@ -25932,7 +25922,7 @@
         <v>77</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>78</v>
@@ -25947,7 +25937,7 @@
         <v>98</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>77</v>
@@ -25956,15 +25946,15 @@
         <v>77</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25987,19 +25977,19 @@
         <v>86</v>
       </c>
       <c r="K204" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L204" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M204" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L204" t="s" s="2">
+      <c r="N204" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M204" t="s" s="2">
+      <c r="O204" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>77</v>
@@ -26048,7 +26038,7 @@
         <v>77</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>78</v>
@@ -26063,7 +26053,7 @@
         <v>98</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>77</v>
@@ -26072,15 +26062,15 @@
         <v>77</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26106,16 +26096,16 @@
         <v>101</v>
       </c>
       <c r="L205" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M205" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N205" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O205" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>77</v>
@@ -26164,7 +26154,7 @@
         <v>77</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>78</v>
@@ -26179,7 +26169,7 @@
         <v>98</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AL205" t="s" s="2">
         <v>77</v>
@@ -26188,15 +26178,15 @@
         <v>77</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26219,13 +26209,13 @@
         <v>77</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -26276,7 +26266,7 @@
         <v>77</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>78</v>
@@ -26305,10 +26295,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -26417,10 +26407,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -26531,14 +26521,14 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
@@ -26560,16 +26550,16 @@
         <v>108</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N209" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>77</v>
@@ -26618,7 +26608,7 @@
         <v>77</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>78</v>
@@ -26647,10 +26637,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -26673,13 +26663,13 @@
         <v>77</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -26730,7 +26720,7 @@
         <v>77</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>85</v>
@@ -26759,10 +26749,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -26788,13 +26778,13 @@
         <v>101</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -26844,7 +26834,7 @@
         <v>77</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>78</v>
@@ -26873,10 +26863,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26899,13 +26889,13 @@
         <v>77</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -26956,7 +26946,7 @@
         <v>77</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>78</v>
@@ -26985,10 +26975,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27097,10 +27087,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -27211,14 +27201,14 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -27240,16 +27230,16 @@
         <v>108</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N215" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O215" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>77</v>
@@ -27298,7 +27288,7 @@
         <v>77</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>78</v>
@@ -27327,10 +27317,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -27356,13 +27346,13 @@
         <v>299</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -27412,7 +27402,7 @@
         <v>77</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>85</v>
@@ -27427,7 +27417,7 @@
         <v>98</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>77</v>
@@ -27436,15 +27426,15 @@
         <v>77</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -27470,13 +27460,13 @@
         <v>299</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
@@ -27526,7 +27516,7 @@
         <v>77</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>78</v>
@@ -27541,7 +27531,7 @@
         <v>98</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL217" t="s" s="2">
         <v>77</v>
@@ -27550,15 +27540,15 @@
         <v>77</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -27581,13 +27571,13 @@
         <v>77</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -27638,7 +27628,7 @@
         <v>77</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>78</v>
@@ -27667,10 +27657,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -27779,10 +27769,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -27893,14 +27883,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -27922,16 +27912,16 @@
         <v>108</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>77</v>
@@ -27980,7 +27970,7 @@
         <v>77</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>78</v>
@@ -28009,10 +27999,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -28038,13 +28028,13 @@
         <v>299</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
@@ -28073,10 +28063,10 @@
         <v>159</v>
       </c>
       <c r="Y222" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>77</v>
@@ -28094,7 +28084,7 @@
         <v>77</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>78</v>
@@ -28109,7 +28099,7 @@
         <v>98</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>77</v>
@@ -28118,15 +28108,15 @@
         <v>77</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -28149,16 +28139,16 @@
         <v>77</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
@@ -28208,7 +28198,7 @@
         <v>77</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>78</v>
@@ -28220,10 +28210,10 @@
         <v>97</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AL223" t="s" s="2">
         <v>77</v>
@@ -28232,15 +28222,15 @@
         <v>77</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -28263,13 +28253,13 @@
         <v>77</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -28320,7 +28310,7 @@
         <v>77</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>78</v>
@@ -28349,10 +28339,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -28461,10 +28451,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -28575,14 +28565,14 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
@@ -28604,16 +28594,16 @@
         <v>108</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N227" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>77</v>
@@ -28662,7 +28652,7 @@
         <v>77</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>78</v>
@@ -28691,10 +28681,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -28720,13 +28710,13 @@
         <v>299</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -28755,10 +28745,10 @@
         <v>159</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>77</v>
@@ -28776,7 +28766,7 @@
         <v>77</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>78</v>
@@ -28791,7 +28781,7 @@
         <v>98</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL228" t="s" s="2">
         <v>77</v>
@@ -28800,15 +28790,15 @@
         <v>77</v>
       </c>
       <c r="AN228" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -28831,16 +28821,16 @@
         <v>77</v>
       </c>
       <c r="K229" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="L229" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M229" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="N229" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
@@ -28890,7 +28880,7 @@
         <v>77</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>78</v>
@@ -28919,10 +28909,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -28945,16 +28935,16 @@
         <v>77</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -29004,7 +28994,7 @@
         <v>77</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>78</v>
@@ -29016,10 +29006,10 @@
         <v>97</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AK230" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AL230" t="s" s="2">
         <v>77</v>
@@ -29033,10 +29023,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -29059,13 +29049,13 @@
         <v>77</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -29116,7 +29106,7 @@
         <v>77</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>78</v>
@@ -29145,10 +29135,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -29257,10 +29247,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -29371,14 +29361,14 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
@@ -29400,16 +29390,16 @@
         <v>108</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N234" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>77</v>
@@ -29458,7 +29448,7 @@
         <v>77</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>78</v>
@@ -29487,10 +29477,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -29513,16 +29503,16 @@
         <v>77</v>
       </c>
       <c r="K235" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L235" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M235" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="N235" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="L235" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
@@ -29572,7 +29562,7 @@
         <v>77</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>85</v>
@@ -29584,10 +29574,10 @@
         <v>97</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AL235" t="s" s="2">
         <v>77</v>
@@ -29601,10 +29591,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -29627,13 +29617,13 @@
         <v>77</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -29684,7 +29674,7 @@
         <v>77</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>78</v>
@@ -29713,10 +29703,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -29825,10 +29815,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -29939,14 +29929,14 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
@@ -29968,16 +29958,16 @@
         <v>108</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N239" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>77</v>
@@ -30026,7 +30016,7 @@
         <v>77</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>78</v>
@@ -30055,10 +30045,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -30084,13 +30074,13 @@
         <v>299</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
@@ -30140,7 +30130,7 @@
         <v>77</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>85</v>
@@ -30155,7 +30145,7 @@
         <v>98</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL240" t="s" s="2">
         <v>77</v>
@@ -30164,15 +30154,15 @@
         <v>77</v>
       </c>
       <c r="AN240" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -30195,13 +30185,13 @@
         <v>77</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -30252,7 +30242,7 @@
         <v>77</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>85</v>
@@ -30281,10 +30271,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -30307,13 +30297,13 @@
         <v>77</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -30364,7 +30354,7 @@
         <v>77</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>78</v>
@@ -30393,10 +30383,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -30505,10 +30495,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -30619,14 +30609,14 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
@@ -30648,16 +30638,16 @@
         <v>108</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N245" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O245" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>77</v>
@@ -30706,7 +30696,7 @@
         <v>77</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>78</v>
@@ -30735,10 +30725,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -30764,13 +30754,13 @@
         <v>299</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
@@ -30820,7 +30810,7 @@
         <v>77</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>85</v>
@@ -30835,7 +30825,7 @@
         <v>98</v>
       </c>
       <c r="AK246" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL246" t="s" s="2">
         <v>77</v>
@@ -30844,15 +30834,15 @@
         <v>77</v>
       </c>
       <c r="AN246" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -30875,13 +30865,13 @@
         <v>77</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -30932,7 +30922,7 @@
         <v>77</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>78</v>
@@ -30961,10 +30951,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -31073,10 +31063,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -31187,14 +31177,14 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E250" s="2"/>
       <c r="F250" t="s" s="2">
@@ -31216,16 +31206,16 @@
         <v>108</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N250" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O250" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>77</v>
@@ -31274,7 +31264,7 @@
         <v>77</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>78</v>
@@ -31303,10 +31293,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -31329,16 +31319,16 @@
         <v>77</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="O251" s="2"/>
       <c r="P251" t="s" s="2">
@@ -31388,7 +31378,7 @@
         <v>77</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>85</v>
@@ -31400,10 +31390,10 @@
         <v>97</v>
       </c>
       <c r="AJ251" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AK251" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AL251" t="s" s="2">
         <v>77</v>
@@ -31412,15 +31402,15 @@
         <v>77</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -31443,16 +31433,16 @@
         <v>77</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
@@ -31481,10 +31471,10 @@
         <v>149</v>
       </c>
       <c r="Y252" t="s" s="2">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="Z252" t="s" s="2">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="AA252" t="s" s="2">
         <v>77</v>
@@ -31502,7 +31492,7 @@
         <v>77</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>78</v>
@@ -31514,10 +31504,10 @@
         <v>97</v>
       </c>
       <c r="AJ252" t="s" s="2">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="AK252" t="s" s="2">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="AL252" t="s" s="2">
         <v>77</v>
@@ -31526,15 +31516,15 @@
         <v>77</v>
       </c>
       <c r="AN252" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -31557,13 +31547,13 @@
         <v>77</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -31614,7 +31604,7 @@
         <v>77</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>78</v>
@@ -31643,10 +31633,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -31755,10 +31745,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -31869,14 +31859,14 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
@@ -31898,16 +31888,16 @@
         <v>108</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N256" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O256" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="P256" t="s" s="2">
         <v>77</v>
@@ -31956,7 +31946,7 @@
         <v>77</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>78</v>
@@ -31985,10 +31975,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -32011,16 +32001,16 @@
         <v>77</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
@@ -32070,7 +32060,7 @@
         <v>77</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>78</v>
@@ -32082,10 +32072,10 @@
         <v>97</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AK257" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AL257" t="s" s="2">
         <v>77</v>
@@ -32094,15 +32084,15 @@
         <v>77</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -32125,16 +32115,16 @@
         <v>77</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
@@ -32184,7 +32174,7 @@
         <v>77</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>78</v>
@@ -32196,10 +32186,10 @@
         <v>97</v>
       </c>
       <c r="AJ258" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AK258" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AL258" t="s" s="2">
         <v>77</v>
@@ -32208,15 +32198,15 @@
         <v>77</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -32239,16 +32229,16 @@
         <v>77</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="O259" s="2"/>
       <c r="P259" t="s" s="2">
@@ -32277,10 +32267,10 @@
         <v>149</v>
       </c>
       <c r="Y259" t="s" s="2">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="Z259" t="s" s="2">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>77</v>
@@ -32298,7 +32288,7 @@
         <v>77</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>78</v>
@@ -32310,10 +32300,10 @@
         <v>97</v>
       </c>
       <c r="AJ259" t="s" s="2">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="AK259" t="s" s="2">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="AL259" t="s" s="2">
         <v>77</v>
@@ -32322,7 +32312,7 @@
         <v>77</v>
       </c>
       <c r="AN259" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationKnowledge.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
